--- a/output/HS_Code_Summary_Brenntag_Specialties_Czech_28511.xlsx
+++ b/output/HS_Code_Summary_Brenntag_Specialties_Czech_28511.xlsx
@@ -50,7 +50,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -70,11 +70,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -109,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -133,12 +128,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -505,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:Q41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -904,145 +897,201 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>ALE: NEOBSAHUJE ČÍSLO CELNÍHO POVOLENÍ (schválený vývozce). Hodnota zásilky 7 497,00 CHF (cca 8 000 EUR) PŘEKRAČUJE limit 6 000 EUR,</t>
+          <t>NEOBSAHUJE ČÍSLO POVOLENÍ SCHVÁLENÉHO VÝVOZCE. Hodnota zásilky 7 497,00 CHF (cca 8 000 EUR) překračuje limit 6 000 EUR, do kterého</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>do kterého smí prohlášení o původu na faktuře učinit kterýkoli vývozce. Nad 6 000 EUR je prohlášení platné POUZE od schváleného vývozce</t>
+          <t>smí prohlášení o původu na faktuře učinit kterýkoli vývozce. Nad 6 000 EUR je platné POUZE od schváleného vývozce s číslem povolení.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>s uvedeným číslem povolení. → V této podobě je preferenční nárok NAPADNUTELNÝ.</t>
+          <t>OVĚŘENO 16.09.2026: LUGAIA AG NENÍ na oficiálním seznamu švýcarských schválených vývozců (BAZG „Swiss Approved Exporters“,</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>ŘEŠENÍ (před podáním JSD): (a) vyžádat od Lugaia AG doplnění čísla povolení schváleného vývozce do věty, NEBO (b) vyžádat průvodní</t>
+          <t>seznam k 15.09.2026, 30 stran – firma se v abecedním pořadí mezi „Ludwig Elkuch“ a „Lumatec SA“ NEVYSKYTUJE).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>osvědčení EUR.1, NEBO (c) proclít bez preference se clem 3. zemí (cca 6,5 % / 3,7 %, tj. cca 480 CHF navíc).</t>
+          <t>→ Lugaia AG tedy ŽÁDNÉ číslo povolení nemá a prohlášení na faktuře NEMŮŽE u této hodnoty platně učinit. Žádat je o doplnění čísla</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Znění věty je navíc nestandardní („swiss-preferential origine“) a chybí místo a datum – doporučuji nechat přepsat na standardní text.</t>
+          <t xml:space="preserve">   do věty NEMÁ SMYSL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>ŘEŠENÍ: (a) vyžádat průvodní osvědčení EUR.1 ověřené švýcarským celním úřadem – jediná reálná cesta k preferenci, NEBO</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>🔴 KRITICKÉ – REX ČÍSLO</t>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        (b) proclít bez preference se clem 3. zemí (cca 6,5 % / 3,7 %, tj. cca 480 CHF navíc).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>NA FAKTUŘE NENÍ ŽÁDNÉ REX ČÍSLO – ani REX, ani jiné číslo celního povolení. Explicitně: REX číslo CHYBÍ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>Pozn.: pro Švýcarsko se REX nepoužívá; relevantní je číslo povolení SCHVÁLENÉHO VÝVOZCE – to na dokladech rovněž CHYBÍ (viz výše).</t>
+          <t>Znění věty je navíc nestandardní („swiss-preferential origine“) a chybí místo a datum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>🔴 KRITICKÉ – REX ČÍSLO</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>⚠️ CCT/VPV KN – ZBOŽÍ BEZ HS KÓDU (odvozeno mnou)</t>
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>NA FAKTUŘE NENÍ ŽÁDNÉ REX ČÍSLO – explicitně: REX číslo CHYBÍ. Není tam ani jiné číslo celního povolení vývozce.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Pos. 7 „packaging“ (1 × 1/2 paleta 80×60×99 cm, 99 kg, 85,00 CHF) NEMÁ v dokladech přiděleno tarifní číslo.</t>
+          <t>POZOR NA ČASTÝ OMYL: REX číslo a preferenční věta NEJSOU ALTERNATIVY. Preferenční věta je TEXT prohlášení o původu; REX číslo</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Zařazeno pravidlem CCT/VPV KN – viz list „Dokumenty a poznámky“.</t>
+          <t>(resp. číslo povolení schváleného vývozce) je OPRÁVNĚNÍ, které se do TÉ VĚTY vepisuje. Správná dvojice tedy není „REX NEBO věta“,</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>VÝSLEDEK: samostatná položka se NEUVÁDÍ – obal se dle VPV 5(b) zařazuje spolu se zbožím; 85,00 CHF vstupuje do celní hodnoty</t>
+          <t>ale „věta S číslem“ (nad 6 000 EUR povinné) vs. „věta BEZ čísla“ (přípustná jen do 6 000 EUR).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>zboží (čl. 71 odst. 1 písm. a) UCC) a je rozpuštěno proporcionálně podle hodnoty (sloupec L).</t>
+          <t>Pro EU–ŠVÝCARSKO se REX NEPOUŽÍVÁ. REX platí pro GSP, CETA (Kanada), Japonsko, Vietnam, Singapur, UK (TCA), Chile, Nový Zéland,</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Záložní varianta, pokud by celní úřad požadoval samostatnou položku (paleta jako zboží): 4415 20 00 (palety ze dřeva), clo 0 %.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Legenda</t>
+          <t>Mercosur aj. Pro Švýcarsko je relevantní institut SCHVÁLENÉHO VÝVOZCE (Ermächtigter Ausführer) – a Lugaia AG jím není (viz výše).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>→ Absence REX čísla zde tedy NENÍ vada sama o sobě; vadou je absence oprávnění schváleného vývozce.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>🔴 ČERVENÁ – kritické zjištění, nutno vyřešit PŘED podáním JSD</t>
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>🔴 POZICE 7 „packaging“ – HS KÓD NENÍ URČEN, NUTNO OVĚŘIT</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>🟠 ORANŽOVÁ – HS kód odvozen pravidlem CCT/VPV KN (nebyl v dokladech)</t>
+          <t>Pos. 7 „packaging“ (1 × 1/2 paleta 80×60×99 cm, 99 kg, 85,00 CHF) NEMÁ v dokladech přiděleno žádné tarifní číslo a materiál obalu</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>CHYBÍ v dokladech – údaj není v žádném z předaných dokumentů; sloupec ponechán záměrně</t>
+          <t>v dokladech rovněž UVEDEN NENÍ. Zařazení této položky proto ZŮSTÁVÁ OTEVŘENÉ – nutno ověřit před podáním JSD.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>CBAM – v zásilce NENÍ žádný CBAM zboží (3920, 3923, 8203 nejsou v příloze I CBAM). Příjemce navíc NENÍ v registru – viz poznámky.</t>
+          <t>Rozbor dle CCT/VPV KN a návrh řešení (NIKOLI potvrzené zařazení) viz list „Dokumenty a poznámky“.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>PRACOVNÍ PŘEDPOKLAD použitý v číslech výše: obal se dle VPV 5(b) nevykazuje samostatně a 85,00 CHF je rozpuštěno do celní hodnoty</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>zboží proporcionálně (sloupec L). Pokud se potvrdí jiné řešení, hodnoty ve sloupcích L a M je nutné přepočítat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>Legenda</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>🔴 ČERVENÁ – kritické zjištění, nutno vyřešit PŘED podáním JSD</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Pos. 7 – HS kód v dokladech není a nebyl dosud určen; rozbor dle CCT/VPV KN je návrh k ověření, ne hotové zařazení</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>CHYBÍ v dokladech – údaj není v žádném z předaných dokumentů; sloupec ponechán záměrně</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>CBAM – v zásilce NENÍ žádný CBAM zboží (3920, 3923, 8203 nejsou v příloze I CBAM). Příjemce navíc NENÍ v registru – viz poznámky.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>ANTIDUMPING – k žádnému z kódů při původu CH nebyla zjištěna antidumpingová opatření.</t>
         </is>
@@ -1060,809 +1109,974 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A125"/>
+  <dimension ref="A1:A152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="165" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11">
+      <c r="A1" s="10">
         <f>== ZÁSILKA ===</f>
         <v/>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Odesílatel (vývozce): Lugaia AG, Industriezone Basper 31, CH-3942 Raron, Švýcarsko. VAT CHE-113.224.199 MWST.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Příjemce (dovozce CZ): Brenntag Specialties Czech a.s., Stachovice 176, CZ-74245 Fulnek.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Faktura / dodací list č. 28511 (DL: L.28511), datum 10.09.2026. Zákazník č. 2816. ZAZ 5339-2. Objednávka OBJ-2026-00182. Reference: Eva Olecká.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Měna faktury: CHF. Celkem 7 497,00 CHF. Platba 30 dní netto.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Zásilka má JEDINÉHO ODESÍLATELE → klasifikace „nejprve dle odesílatele, pak dle HS kódu“ dává 1 blok; HS kódy sloučeny na unikátní v rámci tohoto odesílatele (7 fakturačních pozic → 3 HS kódy).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr"/>
+      <c r="A7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="11">
+      <c r="A8" s="10">
         <f>== PŘIJATÉ DOKUMENTY (stav 16.09.2026) ===</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>✓ COMMERCIAL INVOICE 28511 – POZOR, je označena jako DRAFT (vodoznak). Před podáním JSD vyžádat finální (nedraftovou) fakturu.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>✓ DELIVERY NOTE L.28511</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>✗ CHYBÍ packing list / rozpis hmotností po položkách</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>✗ CHYBÍ doklad o přepravních nákladech Raron (CH) → hranice EU (nutné pro celní hodnotu, viz níže)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>✗ CHYBÍ plná moc k zastupování (pokud dosud nebyla pro Brenntag Specialties Czech a.s. založena)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr"/>
+      <c r="A14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="13">
+      <c r="A15" s="12">
         <f>== 🔴 KRITICKÉ: PREFERENČNÍ VĚTA / COO ===</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Preferenční věta JE PŘÍTOMNA, shodně na faktuře i dodacím listu, pozice 11 „export declaration“:</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  „The exporter of the products covered by this document declares that, except where otherwise clearly indicated,</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   these products are of swiss-preferential origine.“</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>Deklarovaný původ: ŠVÝCARSKO (CH). Při platném prohlášení = preferenční sazba 0 % (Dohoda EU–Švýcarsko / úmluva PEM).</t>
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Deklarovaný původ: ŠVÝCARSKO (CH). Při platném důkazu původu = preferenční sazba 0 % (Dohoda EU–Švýcarsko / úmluva PEM).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr"/>
+      <c r="A20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>PROBLÉM č. 1 – CHYBÍ ČÍSLO CELNÍHO POVOLENÍ:</t>
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>PROBLÉM – VĚTA NENÍ PLATNÁ PRO TUTO HODNOTU ZÁSILKY:</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  Prohlášení o původu na faktuře může bez čísla povolení učinit kterýkoli vývozce POUZE do hodnoty 6 000 EUR na zásilku.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Hodnota této zásilky je 7 497,00 CHF ≈ 8 000 EUR, tedy NAD limitem. Nad 6 000 EUR musí prohlášení učinit SCHVÁLENÝ VÝVOZCE</t>
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Hodnota této zásilky je 7 497,00 CHF (při jakémkoli reálném kurzu cca 7 900–8 000 EUR), tedy NAD limitem.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  a MUSÍ v něm uvést číslo svého celního povolení (srov. korejský vzor: „customs authorization No. 020-12-200186“).</t>
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Nad 6 000 EUR musí prohlášení učinit SCHVÁLENÝ VÝVOZCE a MUSÍ v něm uvést číslo svého celního povolení</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  → Prohlášení v této podobě celní úřad může odmítnout a doměřit clo 3. zemí.</t>
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (srov. korejský vzor: „customs authorization No. 020-12-200186“). Ve větě na dokladech žádné číslo NENÍ.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr"/>
+      <c r="A26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>PROBLÉM č. 2 – NESTANDARDNÍ ZNĚNÍ:</t>
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>OVĚŘENO 16.09.2026 – LUGAIA AG NENÍ SCHVÁLENÝ VÝVOZCE:</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Předepsaný text zní „...these products are of Switzerland preferential origin.“ Doklad uvádí „of swiss-preferential origine“</t>
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Švýcarská celní správa (BAZG) zveřejňuje úplný seznam „Swiss Approved Exporters“ (číslo povolení + název firmy).</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (nesprávný tvar + překlep). Chybí rovněž místo a datum vystavení.</t>
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Prověřen aktuální seznam k 15.09.2026 (30 stran) i předchozí k 30.06.2025: LUGAIA AG V SEZNAMU NENÍ.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr"/>
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  V abecedním pořadí by firma stála mezi „1357 Ludwig Elkuch Aktiengesellschaft“ a „655 Lumatec SA“ – chybí.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>CO OD DODAVATELE VYŽÁDAT (jedna z variant):</t>
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Zdroj: https://www.bazg.admin.ch/en/list-of-swiss-approved-exporters</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (a) opravenou fakturu s prohlášením ve standardním znění a s číslem povolení schváleného vývozce, NEBO</t>
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  → Lugaia AG tedy žádné číslo povolení nemá. ŽÁDAT JE O DOPLNĚNÍ ČÍSLA DO VĚTY NEMÁ SMYSL – nemají co doplnit.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (b) průvodní osvědčení EUR.1 ověřené švýcarským celním úřadem, NEBO</t>
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (Drobná výhrada: seznam uvádí názvy firem v jediném jazyce a povolení může být vedeno na mateřskou společnost.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (c) potvrdit, že preference nebude uplatněna → proclení se clem 3. zemí.</t>
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Pokud by Lugaia tvrdila, že povolení má, ať sdělí jeho číslo a název držitele – ověříme proti seznamu.)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>ŘEŠENÍ – REÁLNĚ JSOU JEN DVĚ MOŽNOSTI:</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (a) Vyžádat PRŮVODNÍ OSVĚDČENÍ EUR.1 ověřené švýcarským celním úřadem – jediná cesta, jak preferenci uplatnit. NEBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (b) Proclít BEZ PREFERENCE se clem 3. zemí.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>FINANČNÍ DOPAD (orientačně): clo 3. zemí cca 6,5 % (3920, 3923) a 3,7 % (8203) z celní hodnoty ≈ 480 CHF navíc oproti preferenci 0 %.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="13">
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>Pozn.: znění věty je navíc nestandardní („of swiss-preferential origine“ místo „of Switzerland preferential origin“), chybí místo a datum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="12">
         <f>== 🔴 KRITICKÉ: REX ČÍSLO ===</f>
         <v/>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="12" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>NA FAKTUŘE NENÍ UVEDENO ŽÁDNÉ REX ČÍSLO. Explicitně konstatuji: REX číslo CHYBÍ.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>Na faktuře ani na dodacím listu není uvedeno ani žádné jiné číslo celního povolení vývozce.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>Metodická poznámka: systém REX (registrovaný vývozce) se na Švýcarsko NEVZTAHUJE – pro EU–CH se používá institut SCHVÁLENÉHO VÝVOZCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>s číslem celního povolení. To na dokladech rovněž chybí, takže preferenční nárok nad 6 000 EUR není podložen (viz výše).</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="12" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="14">
-        <f>== ⚠️ CCT/VPV KN – POLOŽKA BEZ HS KÓDU ===</f>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>Není zde ani žádné jiné číslo celního povolení vývozce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>POZOR NA ČASTÝ OMYL – REX A PREFERENČNÍ VĚTA NEJSOU ALTERNATIVY:</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Preferenční věta = TEXT prohlášení o původu na faktuře.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  REX číslo (resp. číslo povolení schváleného vývozce) = OPRÁVNĚNÍ vývozce takové prohlášení učinit; vepisuje se DO TÉ VĚTY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Nejde tedy o volbu „buď REX, nebo věta“, nýbrž o „věta S číslem“ (nad 6 000 EUR povinné) vs. „věta BEZ čísla“ (jen do 6 000 EUR).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Na této zásilce je tedy stav „věta BEZ čísla“ u zásilky nad limitem – proto je nárok neplatný (viz výše).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>PRO EU–ŠVÝCARSKO SE REX NEPOUŽÍVÁ:</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Systém REX (registrovaný vývozce) se uplatňuje u GSP, CETA (Kanada), Japonska, Vietnamu, Singapuru, UK (TCA), Chile,</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Nového Zélandu, Mercosuru apod. Švýcarsko mezi ně NEPATŘÍ – má vlastní systém SCHVÁLENÝCH VÝVOZCŮ (Ermächtigter Ausführer).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Zdroj: Celní správa ČR, systém REX – https://celnisprava.gov.cz/cz/clo/puvod-zbozi/Stranky/REX-aktualizace.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  → Absence REX čísla na této faktuře tedy sama o sobě NENÍ vadou. Vadou je absence oprávnění schváleného vývozce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="12">
+        <f>== 🔴 POZICE 7 „packaging“ – HS KÓD NENÍ URČEN ===</f>
         <v/>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t>Doklady přiřazují tarifní čísla pouze pozicím 1+2 (3920.1000), 3+4+6 (3923.5090) a 5 (8203.2000).</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t>POZICE 7 „packaging“ (1 × 1/2 paleta 80×60×99 cm – 99 kg, 85,00 CHF) NEMÁ PŘIDĚLENO TARIFNÍ ČÍSLO.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>Zařazeno postupem CCT/VPV KN (reference/Common_Customs_Tariff_EU_CZ.pptx):</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1) CO TO JE?        Přepravní obal zásilky (půlpaleta + balení), nikoli samostatně prodávané zboží; na faktuře jako nákladová položka.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2) Z ČEHO TO JE?    Materiál V DOKLADECH NENÍ UVEDEN (u rozměru 80×60 cm typicky dřevo, příp. plast + stretch fólie/karton).</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3) K ČEMU SLOUŽÍ?   K zabalení a přepravě zboží pozic 1–6; není určeno k samostatnému užití příjemcem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="12" t="inlineStr">
-        <is>
-          <t>Aplikovaná pravidla: VPV 1 + VPV 5(b) – „obalové materiály a obalové schránky předkládané se zbožím v nich se zařazují spolu se zbožím,</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="12" t="inlineStr">
-        <is>
-          <t>pokud jsou takového druhu, který se pro balení tohoto zboží obvykle používá“. Dále čl. 71 odst. 1 písm. a) body ii) a iii) UCC – náklady</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="12" t="inlineStr">
-        <is>
-          <t>na obaly a balení se PŘIČÍTAJÍ k celní hodnotě zboží.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="12" t="inlineStr">
-        <is>
-          <t>→ VÝSLEDEK: pro pos. 7 se NEVYTVÁŘÍ samostatná položka JSD. Částka 85,00 CHF je rozpuštěna do celní hodnoty pozic 1–6 proporcionálně</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   podle hodnoty (faktor 85,00 / 7 412,00 = 0,0114679): 3920 10 25 → 72,59 CHF; 3923 50 90 → 11,38 CHF; 8203 20 00 → 1,03 CHF.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="12" t="inlineStr">
-        <is>
-          <t>→ NEJISTOTA / ZÁLOŽNÍ VARIANTA: druhá věta VPV 5(b) říká, že pravidlo není závazné u obalů zjevně vhodných k opakovanému použití – paleta</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   takovým obalem je. Pokud by celní úřad (nebo dodavatel prodejem palety) vyžadoval samostatnou položku, připadá v úvahu 4415 20 00</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   „Palety, ohradové palety a jiné nakládací plošiny, ze dřeva“, clo 0 %. Vyžaduje potvrzení materiálu palety.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="12" t="inlineStr">
-        <is>
-          <t>→ Toto je JEDINÁ položka, jejíž zařazení jsem odvozoval sám. Vzhledem k nejednoznačnosti doporučuji konzultaci: customs.tariff@mauriceward.com.</t>
-        </is>
-      </c>
-    </row>
     <row r="59">
-      <c r="A59" s="12" t="inlineStr"/>
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>Doklady přiřazují tarifní čísla pouze pozicím 1+2, 3+4+6 a 5.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="11">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>POZICE 7 „packaging“ (1 × 1/2 paleta 80×60×99 cm – 99 kg, 85,00 CHF) NEMÁ PŘIDĚLENO ŽÁDNÉ TARIFNÍ ČÍSLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>a MATERIÁL OBALU NENÍ V DOKLADECH UVEDEN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>→ ZÁVĚR: zařazení této položky NENÍ URČENO a je nutné je před podáním JSD ověřit. Níže uvedený rozbor je NÁVRH, nikoli hotové zařazení.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>Rozbor postupem CCT/VPV KN (reference/Common_Customs_Tariff_EU_CZ.pptx):</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1) CO TO JE?        Přepravní obal zásilky (půlpaleta + balení), na faktuře vystupuje jako nákladová položka, nikoli jako prodané zboží.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2) Z ČEHO TO JE?    NEZNÁMO – materiál v dokladech NENÍ uveden (u rozměru 80×60 cm typicky dřevo, ale může jít i o plast).</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3) K ČEMU SLOUŽÍ?   K zabalení a přepravě zboží pozic 1–6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Na otázku č. 2 tedy nemáme odpověď – a bez ní nelze zařazení uzavřít (deck výslovně požaduje znát odpovědi na všechny tři otázky).</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>NÁVRH K OVĚŘENÍ (varianta A – doporučená): VPV 1 + VPV 5(b) – „obalové materiály a obalové schránky předkládané se zbožím v nich se</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  zařazují spolu se zbožím, pokud jsou takového druhu, který se pro balení tohoto zboží obvykle používá“; dále čl. 71 odst. 1 písm. a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  body ii) a iii) UCC – náklady na obaly a balení se přičítají k celní hodnotě zboží.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  → Pro pos. 7 by se nevytvářela samostatná položka JSD a 85,00 CHF by se rozpustilo do celní hodnoty pozic 1–6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>VARIANTA B: druhá věta VPV 5(b) říká, že pravidlo NENÍ závazné u obalů zjevně vhodných k opakovanému použití – paleta takovým obalem</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  je. Pak by paleta byla samostatnou položkou; je-li dřevěná, připadá v úvahu 4415 20 00 „Palety, ohradové palety a jiné nakládací</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  plošiny, ze dřeva“ (clo 0 %). Vyžaduje potvrzení materiálu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="11" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t>PRACOVNÍ PŘEDPOKLAD V TOMTO SOUBORU: použita varianta A, aby součet odpovídal fakturované částce – faktor 85,00 / 7 412,00 = 0,0114679;</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3920 10 25 → 72,59 CHF; 3923 50 90 → 11,38 CHF; 8203 20 00 → 1,03 CHF. Potvrdí-li se varianta B, je nutné sloupce L a M přepočítat</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  a doplnit čtvrtou položku.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t>CO JE TŘEBA UDĚLAT: (1) zjistit od Lugaia AG materiál obalu/palety a zda je paleta fakturována jako zboží nebo jen jako náklad na balení;</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (2) na základě toho zařazení uzavřít, v případě pochybností konzultovat tarifní tým: customs.tariff@mauriceward.com.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="11" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="10">
         <f>== ODVOZENÍ KN 8 / TARIC 10 U KÓDŮ Z DOKLADŮ ===</f>
         <v/>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="12" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="11" t="inlineStr">
         <is>
           <t>Dodavatel uvedl pouze 6místné HS (3920.1000, 3923.5090, 8203.2000). Pro JSD je nutný 8místný KN / 10místný TARIC – doplněno:</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="11" t="inlineStr">
         <is>
           <t>• 3920.1000 → KN 3920 10 25, TARIC 3920 10 25 90. Cesta: tloušťka 80 µm ≤ 0,125 mm → LDPE, měrná hmotnost &lt; 0,94 → není fólie pro</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  fotorezist (3920 10 23) → není stretch fólie (3920 10 24) → nepotištěná („Print: none“), tedy ne 3920 10 28 → 3920 10 25 „ostatní“.</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="12" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  TARIC: 05 = pro použití v letadlech, 90 = ostatní → 3920 10 25 90.</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="12" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  POZN. K OVĚŘENÍ: linerunit je hadicová (layflat) fólie na roli. Dokud není zpracována na hotové vaky, patří do 3920 jako fólie.</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="12" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  Pokud by byla dodávána jako předem zhotovené vaky/rukávy, přicházelo by v úvahu 3923 21 00. Dle specifikace (role 40/50 m) = 3920.</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="12" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="11" t="inlineStr">
         <is>
           <t>• 3923.5090 → KN 3923 50 90, TARIC 3923 50 90 00 („uzávěry z plastů, jiné než uzávěry a zátky na láhve“).</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="12" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  POZN.: pos. 6 „Suspension Lug“ (závěsné oko) je spíše závěsný prvek než uzávěr; jako součást systému SafeSeal a při hodnotě 2,00 CHF</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="12" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  ponecháno dle deklarace dodavatele. Alternativa 3926 90 97 by byla obhajitelná – dopad nulový.</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="12" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="11" t="inlineStr">
         <is>
           <t>• 8203.2000 → KN 8203 20 00, TARIC 8203 20 00 00 („kleště včetně štípacích, kleštičky, pinzety a podobné ruční nástroje“).</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="12" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="11" t="inlineStr">
         <is>
           <t>Sazby cla uvedené v listu HS Summary jsou ORIENTAČNÍ – před podáním JSD ověřit v TARIC CZ k datu přijetí celního prohlášení.</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="12" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="11">
+    <row r="97">
+      <c r="A97" s="11" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="10">
         <f>== JAZYK POPISU ===</f>
         <v/>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="12" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="11" t="inlineStr">
         <is>
           <t>V ŽÁDNÉM z předaných dokladů NENÍ český popis zboží – doklady jsou pouze anglicky. Dle pravidla „čeština má přednost“ jsem tedy použil</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="12" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="11" t="inlineStr">
         <is>
           <t>fallback: sloupec „Popis zboží (CZ)“ je MŮJ PŘEKLAD / celně-tarifní popis, originální anglické znění je zachováno ve sloupci</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="12" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="11" t="inlineStr">
         <is>
           <t>„Popis dle dokladu (EN)“ pro kontrolu.</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="12" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="13">
+    <row r="102">
+      <c r="A102" s="11" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="12">
         <f>== 🔴 HMOTNOSTI – CHYBĚJÍCÍ ÚDAJE ===</f>
         <v/>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="12" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="11" t="inlineStr">
         <is>
           <t>V dokladech je JEDINÝ hmotnostní údaj: „1 x 1/2 pallet 80x60x99cm - 99Kg“ = HRUBÁ hmotnost celé zásilky včetně palety.</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="12" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="11" t="inlineStr">
         <is>
           <t>• ČISTÁ hmotnost: NENÍ UVEDENA NIKDE – ani celková, ani po položkách.</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="12" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="11" t="inlineStr">
         <is>
           <t>• HRUBÁ hmotnost PO HS KÓDECH: NENÍ UVEDENA – rozpis chybí.</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="12" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="11" t="inlineStr">
         <is>
           <t>Sloupce „Čistá hmotnost“ a „Hrubá hmotnost“ jsou proto ZÁMĚRNĚ PONECHÁNY a označeny „CHYBÍ v dokladech“ – nejsou vyplněny odhadem.</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="12" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="11" t="inlineStr">
         <is>
           <t>ORIENTAČNÍ VÝPOČET (pouze fólie pos. 1+2, z technické specifikace, NIKOLI z dokladu):</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="12" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   pos. 1: 2 × 0,500 m × 40 m × 80 µm × 0,92 g/cm³ × 10 ks = 29,44 kg</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="12" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   pos. 2: 2 × 0,600 m × 50 m × 80 µm × 0,92 g/cm³ × 10 ks = 44,16 kg   → celkem 73,60 kg</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="12" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   (Kontrola věrohodnosti: 73,60 kg fólie + krycí vaky + plomby/krytky/otvírák + paleta ≈ 99 kg hrubé hmotnosti – sedí.)</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="12" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   Hmotnost plomb, krytek a otvíráku NELZE z dokladů odvodit, proto zde odhad neuvádím.</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="12" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="11" t="inlineStr">
         <is>
           <t>→ VYŽÁDAT OD LUGAIA AG PACKING LIST s čistou a hrubou hmotností po položkách. Pro JSD je čistá hmotnost povinný údaj u každé položky.</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="12" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="11">
+    <row r="114">
+      <c r="A114" s="11" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="10">
         <f>== INCOTERM ===</f>
         <v/>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="12" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="11" t="inlineStr">
         <is>
           <t>Uvádím: EXW Raron (Švýcarsko) – shodně v hlavičce faktury i dodacího listu („Shipping Condition: EXW Raron“).</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="12" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="11" t="inlineStr">
         <is>
           <t>⚠️ ROZPOR V DOKLADECH: v pozici 7 (packaging) uvádí DODACÍ LIST „DAP - CZ-74245 Fulnek“, zatímco FAKTURA uvádí „EXW - CZ-74245 Fulnek“.</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="12" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   Kombinace „EXW + místo určení“ je věcně nesmysl. Před podáním JSD nechat dodavatele potvrdit, zda platí EXW Raron nebo DAP Fulnek.</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="12" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="11" t="inlineStr">
         <is>
           <t>DOPAD NA CELNÍ HODNOTU: při EXW Raron NENÍ ve fakturované částce zahrnuta přeprava. Dle čl. 71 UCC se do celní hodnoty PŘIČÍTAJÍ náklady</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="12" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="11" t="inlineStr">
         <is>
           <t>na dopravu a pojištění až na místo vstupu do celního území EU. Fakturovaných 7 497,00 CHF tedy NENÍ konečná celní hodnota – je nutné</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="12" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="11" t="inlineStr">
         <is>
           <t>doplnit dopravné Raron (CH) → hranice EU. Naopak při DAP Fulnek by se vnitrounijní úsek dopravy odečítal.</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="12" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="11">
+    <row r="122">
+      <c r="A122" s="11" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="10">
         <f>== CELNÍ HODNOTA / MĚNA / SLEVA ===</f>
         <v/>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="12" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="11" t="inlineStr">
         <is>
           <t>Fakturováno v CHF. Pro JSD přepočíst celním kurzem platným pro měsíc přijetí celního prohlášení.</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="12" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="11" t="inlineStr">
         <is>
           <t>Rozpis (viz list HS Summary): zboží 7 412,00 CHF + obal 85,00 CHF = 7 497,00 CHF, tj. celá fakturovaná částka je v celní hodnotě.</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="12" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="11" t="inlineStr">
         <is>
           <t>Pos. 6 (vzorek zdarma, 2,00 CHF, „Value for customs purposes only“) – hodnota pro celní účely ponechána, do celní hodnoty se zahrnuje.</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="12" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="11" t="inlineStr">
         <is>
           <t>ŽÁDNÁ OBCHODNÍ SLEVA na faktuře není uvedena → proporcionální rozpuštění slevy se neuplatňuje. Uplatněn pouze proporcionální rozpis obalu.</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="12" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="11">
+    <row r="128">
+      <c r="A128" s="11" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="10">
         <f>== CBAM ===</f>
         <v/>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="12" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="11" t="inlineStr">
         <is>
           <t>V zásilce NENÍ ŽÁDNÉ CBAM ZBOŽÍ. HS kódy 3920 (plasty), 3923 (plasty) a 8203 (ruční nástroje, kap. 82) nejsou v příloze I nařízení CBAM</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="12" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="11" t="inlineStr">
         <is>
           <t>(to pokrývá cement, elektřinu, hnojiva, železo a ocel – kap. 72 a vybrané kódy kap. 73, hliník a vodík). → CBAM se na tuto zásilku NEVZTAHUJE,</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="12" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="11" t="inlineStr">
         <is>
           <t>v JSD se neuvádí žádný Y kód.</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="12" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="11" t="inlineStr">
         <is>
           <t>KONTROLA REGISTRU (provedena i přesto, pro budoucí zásilky): příjemce „Brenntag Specialties Czech a.s.“ (Stachovice 176, CZ-74245 Fulnek)</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="15" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="13" t="inlineStr">
         <is>
           <t>🔴 NENÍ V SOUBORU reference/CBAM_receivers_CZ.xlsx (list List1, 100 záznamů) – hledáno dle názvu firmy i dle obce. Rovněž není mezi</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="12" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   společnostmi mimo EU využívajícími náš sdílený účet CBAM-CZ-2025-QGM67089385721.</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="12" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="11" t="inlineStr">
         <is>
           <t>→ Pro TUTO zásilku to nevadí (žádné CBAM zboží). Pokud ale Brenntag Specialties Czech a.s. bude dovážet CBAM zboží, je třeba zjistit jeho</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="12" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">   CBAM status (Y128 / Y238 / Y137) a doplnit ho do registru. Status jsem neodhadoval.</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="12" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="11">
+    <row r="138">
+      <c r="A138" s="11" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="10">
         <f>== ANTIDUMPING ===</f>
         <v/>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="12" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="11" t="inlineStr">
         <is>
           <t>K žádnému ze tří kódů (3920 10 25, 3923 50 90, 8203 20 00) nebyla při deklarovaném původu ŠVÝCARSKO zjištěna antidumpingová</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="12" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="11" t="inlineStr">
         <is>
           <t>ani vyrovnávací opatření. Antidumpingová opatření jsou vázána na původ zboží – pokud by se potvrdil jiný původ než CH, je nutné ověřit znovu.</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="12" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="11">
+    <row r="142">
+      <c r="A142" s="11" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="10">
         <f>== DALŠÍ KONTROLY PŘED PODÁNÍM JSD ===</f>
         <v/>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="12" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="11" t="inlineStr">
         <is>
           <t>1. Vyžádat FINÁLNÍ fakturu – předaná je označena „DRAFT“.</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="12" t="inlineStr">
-        <is>
-          <t>2. Vyřešit preferenční větu / číslo povolení schváleného vývozce (viz výše) – rozhoduje o cle cca 480 CHF.</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="12" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="11" t="inlineStr">
+        <is>
+          <t>2. Vyžádat od Lugaia AG průvodní osvědčení EUR.1 – Lugaia NENÍ schválený vývozce, věta na faktuře u této hodnoty neplatí.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Bez EUR.1 se proclívá clem 3. zemí (cca 480 CHF navíc).</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="11" t="inlineStr">
         <is>
           <t>3. Vyžádat packing list s čistými hmotnostmi po položkách.</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="12" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="11" t="inlineStr">
         <is>
           <t>4. Potvrdit Incoterm (EXW Raron vs. DAP Fulnek) a doložit dopravné do hranice EU.</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="12" t="inlineStr">
-        <is>
-          <t>5. Potvrdit materiál palety; je-li dřevěná, ověřit aktuální požadavky na dřevěný obalový materiál (ISPM 15) pro dovoz ze Švýcarska.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="12" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="11" t="inlineStr">
+        <is>
+          <t>5. Uzavřít zařazení pos. 7 „packaging“ – zjistit materiál obalu/palety a zda jde o zboží nebo jen náklad na balení.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Je-li paleta dřevěná, ověřit i požadavky na dřevěný obalový materiál (ISPM 15) pro dovoz ze Švýcarska.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="11" t="inlineStr">
         <is>
           <t>6. Ověřit materiál otvíráku SafeSeal (pos. 5) – pro kap. 82 je nutná pracovní část ze základního kovu.</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="12" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="11" t="inlineStr">
         <is>
           <t>7. Ověřit sazby cla a případná opatření v TARIC CZ k datu přijetí celního prohlášení.</t>
         </is>

--- a/output/HS_Code_Summary_Brenntag_Specialties_Czech_28511.xlsx
+++ b/output/HS_Code_Summary_Brenntag_Specialties_Czech_28511.xlsx
@@ -50,7 +50,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +70,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -104,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -124,13 +134,17 @@
     <xf numFmtId="4" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -498,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:Q48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -676,7 +690,7 @@
       <c r="P2" s="2" t="inlineStr"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Clo 3. zemí orientačně 6,5 % (ověřit v TARIC CZ). Preferenčně CH = 0 %, ALE viz kritické upozornění k preferenční větě. Odvození KN 8: LDPE (měrná hmotnost &lt; 0,94), tloušťka 80 µm ≤ 0,125 mm, nepotištěná, nejde o stretch fólii → 3920 10 25; TARIC 90 = ostatní (05 = pro letadla). Bez CBAM, bez antidumpingu.</t>
+          <t>Preferenční sazba CH = 0 % (zásilka je pod limitem CHF 10 300 – lze uplatnit). Bez preference by clo 3. zemí činilo orientačně 6,5 %. Odvození KN 8: LDPE (měrná hmotnost &lt; 0,94), tloušťka 80 µm ≤ 0,125 mm, nepotištěná, nejde o stretch fólii → 3920 10 25; TARIC 90 = ostatní (05 = pro letadla). Bez CBAM, bez antidumpingu.</t>
         </is>
       </c>
     </row>
@@ -876,7 +890,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>🔴 KRITICKÉ – PREFERENČNÍ PŮVOD (preferenční věta)</t>
+          <t>✅ PREFERENČNÍ PŮVOD – PREFERENCI LZE UPLATNIT (oprava dřívějšího závěru)</t>
         </is>
       </c>
     </row>
@@ -897,201 +911,243 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>NEOBSAHUJE ČÍSLO POVOLENÍ SCHVÁLENÉHO VÝVOZCE. Hodnota zásilky 7 497,00 CHF (cca 8 000 EUR) překračuje limit 6 000 EUR, do kterého</t>
+          <t>Věta NEOBSAHUJE číslo povolení schváleného vývozce – a NEMUSÍ, protože zásilka je POD hodnotovým limitem:</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>smí prohlášení o původu na faktuře učinit kterýkoli vývozce. Nad 6 000 EUR je platné POUZE od schváleného vývozce s číslem povolení.</t>
+          <t>ROZHODUJE MĚNA FAKTURY, NIKOLI PŘEPOČET NA EURA. Čl. 30 odst. 2 pravidel původu: zásilka se posuzuje „by reference to the</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>OVĚŘENO 16.09.2026: LUGAIA AG NENÍ na oficiálním seznamu švýcarských schválených vývozců (BAZG „Swiss Approved Exporters“,</t>
+          <t>currency in which the invoice is drawn up, according to the amount fixed by the country concerned“. Faktura je v CHF,</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>seznam k 15.09.2026, 30 stran – firma se v abecedním pořadí mezi „Ludwig Elkuch“ a „Lumatec SA“ NEVYSKYTUJE).</t>
+          <t>platí tedy švýcarská pevná částka: LIMIT = CHF 10 300 (ekvivalent 6 000 EUR). Tyto částky se NESMÍ přepočítávat aktuálním kurzem.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>→ Lugaia AG tedy ŽÁDNÉ číslo povolení nemá a prohlášení na faktuře NEMŮŽE u této hodnoty platně učinit. Žádat je o doplnění čísla</t>
+          <t>FAKTUROVÁNO 7 497,00 CHF &lt; 10 300 CHF → POD LIMITEM, rezerva 2 803 CHF. Prohlášení na faktuře smí učinit KTERÝKOLI vývozce.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   do věty NEMÁ SMYSL.</t>
+          <t>→ Lugaia AG NEMUSÍ být schválený vývozce, číslo povolení se nevyžaduje a EUR.1 NENÍ potřeba. Preferenční sazba 0 %.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>ŘEŠENÍ: (a) vyžádat průvodní osvědčení EUR.1 ověřené švýcarským celním úřadem – jediná reálná cesta k preferenci, NEBO</t>
+          <t>OPRAVA: dřívější verze tohoto souboru počítala limit přepočtem CHF na EUR (cca 8 000 EUR &gt; 6 000 EUR) a chybně dovozovala</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">        (b) proclít bez preference se clem 3. zemí (cca 6,5 % / 3,7 %, tj. cca 480 CHF navíc).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Znění věty je navíc nestandardní („swiss-preferential origine“) a chybí místo a datum.</t>
+          <t>nutnost EUR.1. To byl nesprávný postup – limit se v tomto případě bere v CHF. Riziko cca 480 CHF cla tedy NEPLATÍ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>⚠️ JEDINÁ ZBÝVAJÍCÍ PODMÍNKA – VĚTA MUSÍ BÝT VLASTNORUČNĚ PODEPSÁNA</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>🔴 KRITICKÉ – REX ČÍSLO</t>
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Čl. 18 odst. 5 pravidel původu: „Origin declarations shall bear the original signature of the exporter in manuscript.“</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>NA FAKTUŘE NENÍ ŽÁDNÉ REX ČÍSLO – explicitně: REX číslo CHYBÍ. Není tam ani jiné číslo celního povolení vývozce.</t>
+          <t>Podpisu je zproštěn POUZE schválený vývozce – Lugaia AG jím není (ověřeno v seznamu BAZG „Swiss Approved Exporters“</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>POZOR NA ČASTÝ OMYL: REX číslo a preferenční věta NEJSOU ALTERNATIVY. Preferenční věta je TEXT prohlášení o původu; REX číslo</t>
+          <t>k 15.09.2026: v seznamu NENÍ). Pro ně tedy podpis POVINNÝ JE.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>(resp. číslo povolení schváleného vývozce) je OPRÁVNĚNÍ, které se do TÉ VĚTY vepisuje. Správná dvojice tedy není „REX NEBO věta“,</t>
+          <t>KONTROLA PŘEDANÉ FAKTURY: faktura NENÍ PODEPSÁNA – na str. 3 u preferenční věty není žádný podpis (jediné obrázky v souboru</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>ale „věta S číslem“ (nad 6 000 EUR povinné) vs. „věta BEZ čísla“ (přípustná jen do 6 000 EUR).</t>
+          <t>jsou dlaždice vodoznaku „DRAFT“ na str. 1).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Pro EU–ŠVÝCARSKO se REX NEPOUŽÍVÁ. REX platí pro GSP, CETA (Kanada), Japonsko, Vietnam, Singapur, UK (TCA), Chile, Nový Zéland,</t>
+          <t>→ AKCE: vyžádat od Lugaia AG finální (nedraftovou) fakturu s VLASTNORUČNÍM PODPISEM u preferenční věty. Bez podpisu může</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Mercosur aj. Pro Švýcarsko je relevantní institut SCHVÁLENÉHO VÝVOZCE (Ermächtigter Ausführer) – a Lugaia AG jím není (viz výše).</t>
+          <t xml:space="preserve">   celní úřad prohlášení odmítnout a preference by odpadla.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>→ Absence REX čísla zde tedy NENÍ vada sama o sobě; vadou je absence oprávnění schváleného vývozce.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>🔴 POZICE 7 „packaging“ – HS KÓD NENÍ URČEN, NUTNO OVĚŘIT</t>
+          <t>Drobnost: znění „of swiss-preferential origine“ je nestandardní (předepsáno „of Switzerland preferential origin“). Není to</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>důvod k odmítnutí, ale při opravě faktury je vhodné text rovnou narovnat.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>Pos. 7 „packaging“ (1 × 1/2 paleta 80×60×99 cm, 99 kg, 85,00 CHF) NEMÁ v dokladech přiděleno žádné tarifní číslo a materiál obalu</t>
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>REX ČÍSLO – informativně, není vada</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>v dokladech rovněž UVEDEN NENÍ. Zařazení této položky proto ZŮSTÁVÁ OTEVŘENÉ – nutno ověřit před podáním JSD.</t>
+          <t>Na faktuře NENÍ uvedeno žádné REX číslo – konstatuji explicitně, že REX číslo CHYBÍ.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Rozbor dle CCT/VPV KN a návrh řešení (NIKOLI potvrzené zařazení) viz list „Dokumenty a poznámky“.</t>
+          <t>Pro EU–ŠVÝCARSKO se ale REX NEPOUŽÍVÁ (REX platí pro GSP, CETA, Japonsko, Vietnam, Singapur, UK, Chile, Mercosur aj.).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>PRACOVNÍ PŘEDPOKLAD použitý v číslech výše: obal se dle VPV 5(b) nevykazuje samostatně a 85,00 CHF je rozpuštěno do celní hodnoty</t>
+          <t>Pro Švýcarsko je relevantní institut schváleného vývozce – a ten se u této zásilky nevyžaduje (viz výše).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>zboží proporcionálně (sloupec L). Pokud se potvrdí jiné řešení, hodnoty ve sloupcích L a M je nutné přepočítat.</t>
+          <t>→ Absence REX čísla NENÍ u této zásilky vadou a nemá na clo žádný vliv.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>Legenda</t>
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>🔴 POZICE 7 „packaging“ – HS KÓD NENÍ URČEN, NUTNO OVĚŘIT</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>🔴 ČERVENÁ – kritické zjištění, nutno vyřešit PŘED podáním JSD</t>
+          <t>Pos. 7 „packaging“ (1 × 1/2 paleta 80×60×99 cm, 99 kg, 85,00 CHF) NEMÁ v dokladech přiděleno žádné tarifní číslo a materiál obalu</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>Pos. 7 – HS kód v dokladech není a nebyl dosud určen; rozbor dle CCT/VPV KN je návrh k ověření, ne hotové zařazení</t>
+          <t>v dokladech rovněž UVEDEN NENÍ. Zařazení této položky proto ZŮSTÁVÁ OTEVŘENÉ – nutno ověřit před podáním JSD.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>CHYBÍ v dokladech – údaj není v žádném z předaných dokumentů; sloupec ponechán záměrně</t>
+          <t>Rozbor dle CCT/VPV KN a návrh řešení (NIKOLI potvrzené zařazení) viz list „Dokumenty a poznámky“.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>CBAM – v zásilce NENÍ žádný CBAM zboží (3920, 3923, 8203 nejsou v příloze I CBAM). Příjemce navíc NENÍ v registru – viz poznámky.</t>
+          <t>PRACOVNÍ PŘEDPOKLAD použitý v číslech výše: obal se dle VPV 5(b) nevykazuje samostatně a 85,00 CHF je rozpuštěno do celní hodnoty</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>zboží proporcionálně (sloupec L). Pokud se potvrdí jiné řešení, hodnoty ve sloupcích L a M je nutné přepočítat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>Legenda</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>🔴 ČERVENÁ – nutno vyřešit PŘED podáním JSD   |   ⚠️ ORANŽOVÁ – akce u dodavatele   |   ✅ ZELENÁ – vyřešeno / bez rizika</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Pos. 7 – HS kód v dokladech není a nebyl dosud určen; rozbor dle CCT/VPV KN je návrh k ověření, ne hotové zařazení</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>CHYBÍ v dokladech – údaj není v žádném z předaných dokumentů; sloupec ponechán záměrně</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>CBAM – v zásilce NENÍ žádný CBAM zboží (3920, 3923, 8203 nejsou v příloze I CBAM). Příjemce navíc NENÍ v registru – viz poznámky.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>ANTIDUMPING – k žádnému z kódů při původu CH nebyla zjištěna antidumpingová opatření.</t>
         </is>
@@ -1109,974 +1165,1069 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A152"/>
+  <dimension ref="A1:A167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="165" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10">
+      <c r="A1" s="13">
         <f>== ZÁSILKA ===</f>
         <v/>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Odesílatel (vývozce): Lugaia AG, Industriezone Basper 31, CH-3942 Raron, Švýcarsko. VAT CHE-113.224.199 MWST.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Příjemce (dovozce CZ): Brenntag Specialties Czech a.s., Stachovice 176, CZ-74245 Fulnek.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Faktura / dodací list č. 28511 (DL: L.28511), datum 10.09.2026. Zákazník č. 2816. ZAZ 5339-2. Objednávka OBJ-2026-00182. Reference: Eva Olecká.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Měna faktury: CHF. Celkem 7 497,00 CHF. Platba 30 dní netto.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Zásilka má JEDINÉHO ODESÍLATELE → klasifikace „nejprve dle odesílatele, pak dle HS kódu“ dává 1 blok; HS kódy sloučeny na unikátní v rámci tohoto odesílatele (7 fakturačních pozic → 3 HS kódy).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr"/>
+      <c r="A7" s="14" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="10">
+      <c r="A8" s="13">
         <f>== PŘIJATÉ DOKUMENTY (stav 16.09.2026) ===</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>✓ COMMERCIAL INVOICE 28511 – POZOR, je označena jako DRAFT (vodoznak). Před podáním JSD vyžádat finální (nedraftovou) fakturu.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>✓ DELIVERY NOTE L.28511</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>✗ CHYBÍ packing list / rozpis hmotností po položkách</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>✗ CHYBÍ doklad o přepravních nákladech Raron (CH) → hranice EU (nutné pro celní hodnotu, viz níže)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>✗ CHYBÍ plná moc k zastupování (pokud dosud nebyla pro Brenntag Specialties Czech a.s. založena)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr"/>
+      <c r="A14" s="14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="12">
-        <f>== 🔴 KRITICKÉ: PREFERENČNÍ VĚTA / COO ===</f>
+      <c r="A15" s="13">
+        <f>== ✅ PREFERENČNÍ VĚTA / COO – PREFERENCI LZE UPLATNIT ===</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Preferenční věta JE PŘÍTOMNA, shodně na faktuře i dodacím listu, pozice 11 „export declaration“:</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  „The exporter of the products covered by this document declares that, except where otherwise clearly indicated,</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">   these products are of swiss-preferential origine.“</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>Deklarovaný původ: ŠVÝCARSKO (CH). Při platném důkazu původu = preferenční sazba 0 % (Dohoda EU–Švýcarsko / úmluva PEM).</t>
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>Deklarovaný původ: ŠVÝCARSKO (CH) → preferenční sazba 0 % (Dohoda EU–Švýcarsko / PEM).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr"/>
+      <c r="A20" s="14" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>PROBLÉM – VĚTA NENÍ PLATNÁ PRO TUTO HODNOTU ZÁSILKY:</t>
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>HODNOTOVÝ LIMIT – ROZHODUJE MĚNA FAKTURY, NIKOLI PŘEPOČET NA EURA:</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Prohlášení o původu na faktuře může bez čísla povolení učinit kterýkoli vývozce POUZE do hodnoty 6 000 EUR na zásilku.</t>
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Prohlášení o původu na faktuře smí bez čísla povolení učinit KTERÝKOLI vývozce do stanoveného hodnotového limitu</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Hodnota této zásilky je 7 497,00 CHF (při jakémkoli reálném kurzu cca 7 900–8 000 EUR), tedy NAD limitem.</t>
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (čl. 18 odst. 1 písm. b) pravidel původu – „originating products the total value of which does not exceed EUR 6 000“).</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Nad 6 000 EUR musí prohlášení učinit SCHVÁLENÝ VÝVOZCE a MUSÍ v něm uvést číslo svého celního povolení</t>
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Čl. 30 odst. 2 týchž pravidel ale výslovně stanoví, že se zásilka posuzuje</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (srov. korejský vzor: „customs authorization No. 020-12-200186“). Ve větě na dokladech žádné číslo NENÍ.</t>
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     „by reference to the CURRENCY IN WHICH THE INVOICE IS DRAWN UP, according to the amount fixed by the country concerned“.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr"/>
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Každá země si pevně stanoví ekvivalent 6 000 EUR ve své měně a tyto pevné částky se NESMÍ přepočítávat aktuálním kurzem</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>OVĚŘENO 16.09.2026 – LUGAIA AG NENÍ SCHVÁLENÝ VÝVOZCE:</t>
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  („dürfen nicht mit dem aktuellen Währungskurs umgerechnet werden“).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Švýcarská celní správa (BAZG) zveřejňuje úplný seznam „Swiss Approved Exporters“ (číslo povolení + název firmy).</t>
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Švýcarská pevná částka: 6 000 EUR = CHF 10 300.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Prověřen aktuální seznam k 15.09.2026 (30 stran) i předchozí k 30.06.2025: LUGAIA AG V SEZNAMU NENÍ.</t>
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FAKTURA JE V CHF → PLATÍ LIMIT CHF 10 300.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  V abecedním pořadí by firma stála mezi „1357 Ludwig Elkuch Aktiengesellschaft“ a „655 Lumatec SA“ – chybí.</t>
-        </is>
-      </c>
+      <c r="A30" s="14" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Fakturovaná hodnota: 7 497,00 CHF (z toho zboží 7 412,00 CHF + obal 85,00 CHF).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7 497,00 CHF &lt; 10 300,00 CHF → ZÁSILKA JE POD LIMITEM, rezerva 2 803,00 CHF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>ZÁVĚR: prohlášení na faktuře smí učinit kterýkoli vývozce. Lugaia AG NEMUSÍ být schválený vývozce, číslo celního povolení</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  se ve větě NEVYŽADUJE a PRŮVODNÍ OSVĚDČENÍ EUR.1 NENÍ POTŘEBA. Preferenční sazba 0 % je uplatnitelná.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (To, že Lugaia AG není v seznamu švýcarských schválených vývozců BAZG k 15.09.2026, je tedy v pořádku a očekávané –</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   pro zásilky pod limitem status schváleného vývozce nepotřebuje.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>⚠️ OPRAVA DŘÍVĚJŠÍHO ZÁVĚRU: první verze tohoto souboru převedla 7 497 CHF na cca 8 000 EUR, porovnala s limitem 6 000 EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  a dovodila, že je nutné EUR.1 a že hrozí doměření cca 480 CHF cla. TO BYLO CHYBNĚ – limit se u faktury v CHF bere v CHF</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (10 300) a přepočet kurzem je výslovně vyloučen. Riziko 480 CHF NEPLATÍ, EUR.1 se nevyžaduje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Zdroje: čl. 18 a 30 pravidel původu (EFTA, Appendix A k revidované úmluvě PEM); BAZG FAQ Freihandel/präferenzieller Ursprung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="15">
+        <f>== ⚠️ ZBÝVÁ VYŘEŠIT: PODPIS NA PREFERENČNÍ VĚTĚ ===</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>Čl. 18 odst. 5 pravidel původu: „Origin declarations shall bear the ORIGINAL SIGNATURE OF THE EXPORTER IN MANUSCRIPT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  However, an approved exporter within the meaning of Article 19 shall not be required to sign such declarations...“</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>→ Podpisu je zproštěn POUZE schválený vývozce. Lugaia AG schváleným vývozcem NENÍ (ověřeno v seznamu BAZG „Swiss Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Exporters“ k 15.09.2026 i v edici k 30.06.2025 – firma tam není; abecedně by stála mezi „Ludwig Elkuch“ a „Lumatec SA“).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  Zdroj: https://www.bazg.admin.ch/en/list-of-swiss-approved-exporters</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  → Lugaia AG tedy žádné číslo povolení nemá. ŽÁDAT JE O DOPLNĚNÍ ČÍSLA DO VĚTY NEMÁ SMYSL – nemají co doplnit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (Drobná výhrada: seznam uvádí názvy firem v jediném jazyce a povolení může být vedeno na mateřskou společnost.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Pokud by Lugaia tvrdila, že povolení má, ať sdělí jeho číslo a název držitele – ověříme proti seznamu.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
-        <is>
-          <t>ŘEŠENÍ – REÁLNĚ JSOU JEN DVĚ MOŽNOSTI:</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (a) Vyžádat PRŮVODNÍ OSVĚDČENÍ EUR.1 ověřené švýcarským celním úřadem – jediná cesta, jak preferenci uplatnit. NEBO</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (b) Proclít BEZ PREFERENCE se clem 3. zemí.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>FINANČNÍ DOPAD (orientačně): clo 3. zemí cca 6,5 % (3920, 3923) a 3,7 % (8203) z celní hodnoty ≈ 480 CHF navíc oproti preferenci 0 %.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>Pozn.: znění věty je navíc nestandardní („of swiss-preferential origine“ místo „of Switzerland preferential origin“), chybí místo a datum.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="12">
-        <f>== 🔴 KRITICKÉ: REX ČÍSLO ===</f>
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>→ Pro Lugaia AG je tedy VLASTNORUČNÍ PODPIS pod preferenční větou POVINNÝ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>KONTROLA PŘEDANÉ FAKTURY: FAKTURA NENÍ PODEPSÁNA. Na str. 3, kde je preferenční věta, není žádný podpis ani podpisový blok;</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  jediné obrázky v PDF jsou dlaždice vodoznaku „DRAFT“ na str. 1. Dodací list rovněž bez podpisu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>AKCE: vyžádat od Lugaia AG finální (nedraftovou) fakturu s vlastnoručním podpisem u preferenční věty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Bez podpisu může celní úřad prohlášení odmítnout a preference by odpadla (pak clo 3. zemí cca 6,5 % / 3,7 %, tj. cca 480 CHF).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>DROBNOST K NARÁVNÁNÍ PŘI OPRAVĚ FAKTURY: znění „these products are of swiss-preferential origine“ je nestandardní –</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  předepsané znění je „...these products are of Switzerland preferential origin.“ Samo o sobě to není důvod k odmítnutí.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="13">
+        <f>== UMÍSTĚNÍ PREFERENČNÍ VĚTY (invoice vs. packing list) ===</f>
         <v/>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>Čl. 18 odst. 4 pravidel původu: prohlášení se vyhotovuje „on the INVOICE, the DELIVERY NOTE or ANOTHER COMMERCIAL DOCUMENT“.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>Faktura, dodací list i packing list jsou tedy právně přípustné – podmínkou je, že doklad popisuje zboží dostatečně podrobně,</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t>aby je bylo možné identifikovat, a že jej vystavuje vývozce (přepravní doklad typu CMR či B/L proto nevyhovuje).</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="14" t="inlineStr">
+        <is>
+          <t>PRAKTICKY: větu chceme vždy vidět NA FAKTUŘE – to je doklad předkládaný k celnímu prohlášení.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="14" t="inlineStr">
+        <is>
+          <t>U této zásilky je věta na faktuře i na dodacím listu, ve shodném znění → z hlediska umístění je vše v pořádku.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="13">
+        <f>== REX ČÍSLO – informativně ===</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="14" t="inlineStr">
         <is>
           <t>NA FAKTUŘE NENÍ UVEDENO ŽÁDNÉ REX ČÍSLO. Explicitně konstatuji: REX číslo CHYBÍ.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>Není zde ani žádné jiné číslo celního povolení vývozce.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>POZOR NA ČASTÝ OMYL – REX A PREFERENČNÍ VĚTA NEJSOU ALTERNATIVY:</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Preferenční věta = TEXT prohlášení o původu na faktuře.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  REX číslo (resp. číslo povolení schváleného vývozce) = OPRÁVNĚNÍ vývozce takové prohlášení učinit; vepisuje se DO TÉ VĚTY.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Nejde tedy o volbu „buď REX, nebo věta“, nýbrž o „věta S číslem“ (nad 6 000 EUR povinné) vs. „věta BEZ čísla“ (jen do 6 000 EUR).</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Na této zásilce je tedy stav „věta BEZ čísla“ u zásilky nad limitem – proto je nárok neplatný (viz výše).</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t>PRO EU–ŠVÝCARSKO SE REX NEPOUŽÍVÁ:</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Systém REX (registrovaný vývozce) se uplatňuje u GSP, CETA (Kanada), Japonska, Vietnamu, Singapuru, UK (TCA), Chile,</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Nového Zélandu, Mercosuru apod. Švýcarsko mezi ně NEPATŘÍ – má vlastní systém SCHVÁLENÝCH VÝVOZCŮ (Ermächtigter Ausführer).</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Zdroj: Celní správa ČR, systém REX – https://celnisprava.gov.cz/cz/clo/puvod-zbozi/Stranky/REX-aktualizace.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  → Absence REX čísla na této faktuře tedy sama o sobě NENÍ vadou. Vadou je absence oprávnění schváleného vývozce.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="11" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="12">
+    <row r="68">
+      <c r="A68" s="14" t="inlineStr">
+        <is>
+          <t>Pro EU–Švýcarsko se však systém REX NEPOUŽÍVÁ – platí pro GSP, CETA (Kanada), Japonsko, Vietnam, Singapur, UK (TCA), Chile,</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="14" t="inlineStr">
+        <is>
+          <t>Nový Zéland, Mercosur apod. Švýcarsko má vlastní systém schválených vývozců, který se u zásilky pod limitem nevyžaduje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="14" t="inlineStr">
+        <is>
+          <t>Zdroj: Celní správa ČR – https://celnisprava.gov.cz/cz/clo/puvod-zbozi/Stranky/REX-aktualizace.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="14" t="inlineStr">
+        <is>
+          <t>→ Absence REX čísla NENÍ u této zásilky vadou a na clo nemá vliv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="14" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="16">
         <f>== 🔴 POZICE 7 „packaging“ – HS KÓD NENÍ URČEN ===</f>
         <v/>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="11" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="14" t="inlineStr">
         <is>
           <t>Doklady přiřazují tarifní čísla pouze pozicím 1+2, 3+4+6 a 5.</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="11" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="14" t="inlineStr">
         <is>
           <t>POZICE 7 „packaging“ (1 × 1/2 paleta 80×60×99 cm – 99 kg, 85,00 CHF) NEMÁ PŘIDĚLENO ŽÁDNÉ TARIFNÍ ČÍSLO</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="11" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="14" t="inlineStr">
         <is>
           <t>a MATERIÁL OBALU NENÍ V DOKLADECH UVEDEN.</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="11" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="14" t="inlineStr">
         <is>
           <t>→ ZÁVĚR: zařazení této položky NENÍ URČENO a je nutné je před podáním JSD ověřit. Níže uvedený rozbor je NÁVRH, nikoli hotové zařazení.</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="11" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="11" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="14" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="14" t="inlineStr">
         <is>
           <t>Rozbor postupem CCT/VPV KN (reference/Common_Customs_Tariff_EU_CZ.pptx):</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="11" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  1) CO TO JE?        Přepravní obal zásilky (půlpaleta + balení), na faktuře vystupuje jako nákladová položka, nikoli jako prodané zboží.</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="11" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  2) Z ČEHO TO JE?    NEZNÁMO – materiál v dokladech NENÍ uveden (u rozměru 80×60 cm typicky dřevo, ale může jít i o plast).</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="11" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  3) K ČEMU SLOUŽÍ?   K zabalení a přepravě zboží pozic 1–6.</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="11" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  Na otázku č. 2 tedy nemáme odpověď – a bez ní nelze zařazení uzavřít (deck výslovně požaduje znát odpovědi na všechny tři otázky).</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="11" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="11" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="14" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="14" t="inlineStr">
         <is>
           <t>NÁVRH K OVĚŘENÍ (varianta A – doporučená): VPV 1 + VPV 5(b) – „obalové materiály a obalové schránky předkládané se zbožím v nich se</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="11" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  zařazují spolu se zbožím, pokud jsou takového druhu, který se pro balení tohoto zboží obvykle používá“; dále čl. 71 odst. 1 písm. a)</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="11" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  body ii) a iii) UCC – náklady na obaly a balení se přičítají k celní hodnotě zboží.</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="11" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  → Pro pos. 7 by se nevytvářela samostatná položka JSD a 85,00 CHF by se rozpustilo do celní hodnoty pozic 1–6.</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="11" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="14" t="inlineStr">
         <is>
           <t>VARIANTA B: druhá věta VPV 5(b) říká, že pravidlo NENÍ závazné u obalů zjevně vhodných k opakovanému použití – paleta takovým obalem</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="11" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  je. Pak by paleta byla samostatnou položkou; je-li dřevěná, připadá v úvahu 4415 20 00 „Palety, ohradové palety a jiné nakládací</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="11" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  plošiny, ze dřeva“ (clo 0 %). Vyžaduje potvrzení materiálu.</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="11" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="11" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="14" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="14" t="inlineStr">
         <is>
           <t>PRACOVNÍ PŘEDPOKLAD V TOMTO SOUBORU: použita varianta A, aby součet odpovídal fakturované částce – faktor 85,00 / 7 412,00 = 0,0114679;</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="11" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  3920 10 25 → 72,59 CHF; 3923 50 90 → 11,38 CHF; 8203 20 00 → 1,03 CHF. Potvrdí-li se varianta B, je nutné sloupce L a M přepočítat</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="11" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  a doplnit čtvrtou položku.</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="11" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="11" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="14" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="14" t="inlineStr">
         <is>
           <t>CO JE TŘEBA UDĚLAT: (1) zjistit od Lugaia AG materiál obalu/palety a zda je paleta fakturována jako zboží nebo jen jako náklad na balení;</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="11" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  (2) na základě toho zařazení uzavřít, v případě pochybností konzultovat tarifní tým: customs.tariff@mauriceward.com.</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="11" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="10">
+    <row r="99">
+      <c r="A99" s="14" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="13">
         <f>== ODVOZENÍ KN 8 / TARIC 10 U KÓDŮ Z DOKLADŮ ===</f>
         <v/>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="11" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="14" t="inlineStr">
         <is>
           <t>Dodavatel uvedl pouze 6místné HS (3920.1000, 3923.5090, 8203.2000). Pro JSD je nutný 8místný KN / 10místný TARIC – doplněno:</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="11" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="14" t="inlineStr">
         <is>
           <t>• 3920.1000 → KN 3920 10 25, TARIC 3920 10 25 90. Cesta: tloušťka 80 µm ≤ 0,125 mm → LDPE, měrná hmotnost &lt; 0,94 → není fólie pro</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="11" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  fotorezist (3920 10 23) → není stretch fólie (3920 10 24) → nepotištěná („Print: none“), tedy ne 3920 10 28 → 3920 10 25 „ostatní“.</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="11" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  TARIC: 05 = pro použití v letadlech, 90 = ostatní → 3920 10 25 90.</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="11" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  POZN. K OVĚŘENÍ: linerunit je hadicová (layflat) fólie na roli. Dokud není zpracována na hotové vaky, patří do 3920 jako fólie.</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="11" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  Pokud by byla dodávána jako předem zhotovené vaky/rukávy, přicházelo by v úvahu 3923 21 00. Dle specifikace (role 40/50 m) = 3920.</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="11" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="14" t="inlineStr">
         <is>
           <t>• 3923.5090 → KN 3923 50 90, TARIC 3923 50 90 00 („uzávěry z plastů, jiné než uzávěry a zátky na láhve“).</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="11" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  POZN.: pos. 6 „Suspension Lug“ (závěsné oko) je spíše závěsný prvek než uzávěr; jako součást systému SafeSeal a při hodnotě 2,00 CHF</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="11" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  ponecháno dle deklarace dodavatele. Alternativa 3926 90 97 by byla obhajitelná – dopad nulový.</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="11" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="14" t="inlineStr">
         <is>
           <t>• 8203.2000 → KN 8203 20 00, TARIC 8203 20 00 00 („kleště včetně štípacích, kleštičky, pinzety a podobné ruční nástroje“).</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="11" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="14" t="inlineStr">
         <is>
           <t>Sazby cla uvedené v listu HS Summary jsou ORIENTAČNÍ – před podáním JSD ověřit v TARIC CZ k datu přijetí celního prohlášení.</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="11" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="10">
+    <row r="112">
+      <c r="A112" s="14" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="13">
         <f>== JAZYK POPISU ===</f>
         <v/>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="11" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="14" t="inlineStr">
         <is>
           <t>V ŽÁDNÉM z předaných dokladů NENÍ český popis zboží – doklady jsou pouze anglicky. Dle pravidla „čeština má přednost“ jsem tedy použil</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="11" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="14" t="inlineStr">
         <is>
           <t>fallback: sloupec „Popis zboží (CZ)“ je MŮJ PŘEKLAD / celně-tarifní popis, originální anglické znění je zachováno ve sloupci</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="11" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="14" t="inlineStr">
         <is>
           <t>„Popis dle dokladu (EN)“ pro kontrolu.</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="11" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="12">
+    <row r="117">
+      <c r="A117" s="14" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="16">
         <f>== 🔴 HMOTNOSTI – CHYBĚJÍCÍ ÚDAJE ===</f>
         <v/>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="11" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="14" t="inlineStr">
         <is>
           <t>V dokladech je JEDINÝ hmotnostní údaj: „1 x 1/2 pallet 80x60x99cm - 99Kg“ = HRUBÁ hmotnost celé zásilky včetně palety.</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="11" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="14" t="inlineStr">
         <is>
           <t>• ČISTÁ hmotnost: NENÍ UVEDENA NIKDE – ani celková, ani po položkách.</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="11" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="14" t="inlineStr">
         <is>
           <t>• HRUBÁ hmotnost PO HS KÓDECH: NENÍ UVEDENA – rozpis chybí.</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="11" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="14" t="inlineStr">
         <is>
           <t>Sloupce „Čistá hmotnost“ a „Hrubá hmotnost“ jsou proto ZÁMĚRNĚ PONECHÁNY a označeny „CHYBÍ v dokladech“ – nejsou vyplněny odhadem.</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="11" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="14" t="inlineStr">
         <is>
           <t>ORIENTAČNÍ VÝPOČET (pouze fólie pos. 1+2, z technické specifikace, NIKOLI z dokladu):</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="11" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">   pos. 1: 2 × 0,500 m × 40 m × 80 µm × 0,92 g/cm³ × 10 ks = 29,44 kg</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="11" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">   pos. 2: 2 × 0,600 m × 50 m × 80 µm × 0,92 g/cm³ × 10 ks = 44,16 kg   → celkem 73,60 kg</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="11" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">   (Kontrola věrohodnosti: 73,60 kg fólie + krycí vaky + plomby/krytky/otvírák + paleta ≈ 99 kg hrubé hmotnosti – sedí.)</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="11" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">   Hmotnost plomb, krytek a otvíráku NELZE z dokladů odvodit, proto zde odhad neuvádím.</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="11" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="14" t="inlineStr">
         <is>
           <t>→ VYŽÁDAT OD LUGAIA AG PACKING LIST s čistou a hrubou hmotností po položkách. Pro JSD je čistá hmotnost povinný údaj u každé položky.</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="11" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="10">
+    <row r="129">
+      <c r="A129" s="14" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="13">
         <f>== INCOTERM ===</f>
         <v/>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="11" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="14" t="inlineStr">
         <is>
           <t>Uvádím: EXW Raron (Švýcarsko) – shodně v hlavičce faktury i dodacího listu („Shipping Condition: EXW Raron“).</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="11" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="14" t="inlineStr">
         <is>
           <t>⚠️ ROZPOR V DOKLADECH: v pozici 7 (packaging) uvádí DODACÍ LIST „DAP - CZ-74245 Fulnek“, zatímco FAKTURA uvádí „EXW - CZ-74245 Fulnek“.</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="11" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">   Kombinace „EXW + místo určení“ je věcně nesmysl. Před podáním JSD nechat dodavatele potvrdit, zda platí EXW Raron nebo DAP Fulnek.</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="11" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="14" t="inlineStr">
         <is>
           <t>DOPAD NA CELNÍ HODNOTU: při EXW Raron NENÍ ve fakturované částce zahrnuta přeprava. Dle čl. 71 UCC se do celní hodnoty PŘIČÍTAJÍ náklady</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="11" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="14" t="inlineStr">
         <is>
           <t>na dopravu a pojištění až na místo vstupu do celního území EU. Fakturovaných 7 497,00 CHF tedy NENÍ konečná celní hodnota – je nutné</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="11" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="14" t="inlineStr">
         <is>
           <t>doplnit dopravné Raron (CH) → hranice EU. Naopak při DAP Fulnek by se vnitrounijní úsek dopravy odečítal.</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="11" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="10">
+    <row r="137">
+      <c r="A137" s="14" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="13">
         <f>== CELNÍ HODNOTA / MĚNA / SLEVA ===</f>
         <v/>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="11" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="14" t="inlineStr">
         <is>
           <t>Fakturováno v CHF. Pro JSD přepočíst celním kurzem platným pro měsíc přijetí celního prohlášení.</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="11" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="14" t="inlineStr">
         <is>
           <t>Rozpis (viz list HS Summary): zboží 7 412,00 CHF + obal 85,00 CHF = 7 497,00 CHF, tj. celá fakturovaná částka je v celní hodnotě.</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="11" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="14" t="inlineStr">
         <is>
           <t>Pos. 6 (vzorek zdarma, 2,00 CHF, „Value for customs purposes only“) – hodnota pro celní účely ponechána, do celní hodnoty se zahrnuje.</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="11" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="14" t="inlineStr">
         <is>
           <t>ŽÁDNÁ OBCHODNÍ SLEVA na faktuře není uvedena → proporcionální rozpuštění slevy se neuplatňuje. Uplatněn pouze proporcionální rozpis obalu.</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="11" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="10">
+    <row r="143">
+      <c r="A143" s="14" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="13">
         <f>== CBAM ===</f>
         <v/>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="11" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="14" t="inlineStr">
         <is>
           <t>V zásilce NENÍ ŽÁDNÉ CBAM ZBOŽÍ. HS kódy 3920 (plasty), 3923 (plasty) a 8203 (ruční nástroje, kap. 82) nejsou v příloze I nařízení CBAM</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="11" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="14" t="inlineStr">
         <is>
           <t>(to pokrývá cement, elektřinu, hnojiva, železo a ocel – kap. 72 a vybrané kódy kap. 73, hliník a vodík). → CBAM se na tuto zásilku NEVZTAHUJE,</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="11" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="14" t="inlineStr">
         <is>
           <t>v JSD se neuvádí žádný Y kód.</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="11" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="14" t="inlineStr">
         <is>
           <t>KONTROLA REGISTRU (provedena i přesto, pro budoucí zásilky): příjemce „Brenntag Specialties Czech a.s.“ (Stachovice 176, CZ-74245 Fulnek)</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="13" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="17" t="inlineStr">
         <is>
           <t>🔴 NENÍ V SOUBORU reference/CBAM_receivers_CZ.xlsx (list List1, 100 záznamů) – hledáno dle názvu firmy i dle obce. Rovněž není mezi</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="11" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">   společnostmi mimo EU využívajícími náš sdílený účet CBAM-CZ-2025-QGM67089385721.</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="11" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="14" t="inlineStr">
         <is>
           <t>→ Pro TUTO zásilku to nevadí (žádné CBAM zboží). Pokud ale Brenntag Specialties Czech a.s. bude dovážet CBAM zboží, je třeba zjistit jeho</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="11" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">   CBAM status (Y128 / Y238 / Y137) a doplnit ho do registru. Status jsem neodhadoval.</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="11" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="10">
+    <row r="153">
+      <c r="A153" s="14" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="13">
         <f>== ANTIDUMPING ===</f>
         <v/>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="11" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="14" t="inlineStr">
         <is>
           <t>K žádnému ze tří kódů (3920 10 25, 3923 50 90, 8203 20 00) nebyla při deklarovaném původu ŠVÝCARSKO zjištěna antidumpingová</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="11" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="14" t="inlineStr">
         <is>
           <t>ani vyrovnávací opatření. Antidumpingová opatření jsou vázána na původ zboží – pokud by se potvrdil jiný původ než CH, je nutné ověřit znovu.</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="11" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="10">
+    <row r="157">
+      <c r="A157" s="14" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="13">
         <f>== DALŠÍ KONTROLY PŘED PODÁNÍM JSD ===</f>
         <v/>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="11" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="14" t="inlineStr">
         <is>
           <t>1. Vyžádat FINÁLNÍ fakturu – předaná je označena „DRAFT“.</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="11" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="14" t="inlineStr">
         <is>
           <t>2. Vyžádat od Lugaia AG průvodní osvědčení EUR.1 – Lugaia NENÍ schválený vývozce, věta na faktuře u této hodnoty neplatí.</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="11" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">   Bez EUR.1 se proclívá clem 3. zemí (cca 480 CHF navíc).</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="11" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="14" t="inlineStr">
         <is>
           <t>3. Vyžádat packing list s čistými hmotnostmi po položkách.</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="11" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="14" t="inlineStr">
         <is>
           <t>4. Potvrdit Incoterm (EXW Raron vs. DAP Fulnek) a doložit dopravné do hranice EU.</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="11" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="14" t="inlineStr">
         <is>
           <t>5. Uzavřít zařazení pos. 7 „packaging“ – zjistit materiál obalu/palety a zda jde o zboží nebo jen náklad na balení.</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="11" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">   Je-li paleta dřevěná, ověřit i požadavky na dřevěný obalový materiál (ISPM 15) pro dovoz ze Švýcarska.</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="11" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="14" t="inlineStr">
         <is>
           <t>6. Ověřit materiál otvíráku SafeSeal (pos. 5) – pro kap. 82 je nutná pracovní část ze základního kovu.</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="11" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="14" t="inlineStr">
         <is>
           <t>7. Ověřit sazby cla a případná opatření v TARIC CZ k datu přijetí celního prohlášení.</t>
         </is>
